--- a/health_coach_forms/005_yoga_registration_and_waiver_form--health_coach_forms.xlsx
+++ b/health_coach_forms/005_yoga_registration_and_waiver_form--health_coach_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'allergies'}</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Allergies'}</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'high_blood_pressure'}</t>
+          <t>high_blood_pressure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'High Blood Pressure'}</t>
+          <t>High Blood Pressure</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'high_cholesterol'}</t>
+          <t>high_cholesterol</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'High Cholesterol'}</t>
+          <t>High Cholesterol</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'epilepsy'}</t>
+          <t>epilepsy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Epilepsy'}</t>
+          <t>Epilepsy</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'severe_headaches'}</t>
+          <t>severe_headaches</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Severe Headaches'}</t>
+          <t>Severe Headaches</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'severe_migraines'}</t>
+          <t>severe_migraines</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Severe Migraines'}</t>
+          <t>Severe Migraines</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'seizures'}</t>
+          <t>seizures</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Seizures'}</t>
+          <t>Seizures</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'asthma'}</t>
+          <t>asthma</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Asthma'}</t>
+          <t>Asthma</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'chronic_back_pain'}</t>
+          <t>chronic_back_pain</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Chronic Back Pain'}</t>
+          <t>Chronic Back Pain</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'mother'}</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Mother'}</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'father'}</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Father'}</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'provided'}</t>
+          <t>provided</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Provided'}</t>
+          <t>Provided</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'not_provided'}</t>
+          <t>not_provided</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Not Provided'}</t>
+          <t>Not Provided</t>
         </is>
       </c>
     </row>
